--- a/report_forms/015_platform_metrics_report_form--report_forms.xlsx
+++ b/report_forms/015_platform_metrics_report_form--report_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -845,7 +845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'q1_2024'}</t>
+          <t>q1_2024</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Q1 2024'}</t>
+          <t>Q1 2024</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'q2_2024'}</t>
+          <t>q2_2024</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Q2 2024'}</t>
+          <t>Q2 2024</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'q3_2024'}</t>
+          <t>q3_2024</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'Q3 2024'}</t>
+          <t>Q3 2024</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'name':_'q4_2024'}</t>
+          <t>q4_2024</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'name': 'Q4 2024'}</t>
+          <t>Q4 2024</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'i_have_read_and_understand_the_terms_of_this_form_submission'}</t>
+          <t>i_have_read_and_understand_the_terms_of_this_form_submission</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'I have read and understand the terms of this form submission'}</t>
+          <t>I have read and understand the terms of this form submission</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'i_understand_that_this_form_submission_is_used_for_internal_purposes_only'}</t>
+          <t>i_understand_that_this_form_submission_is_used_for_internal_purposes_only</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'I understand that this form submission is used for internal purposes only'}</t>
+          <t>I understand that this form submission is used for internal purposes only</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'platform_metrics_report_form_submit_confirmation'}</t>
+          <t>platform_metrics_report_form_submit_confirmation</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'platform_metrics_report_form_submit_confirmation'}</t>
+          <t>platform metrics report form submit confirmation</t>
         </is>
       </c>
     </row>
@@ -997,29 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'platform_metrics_report_form_submit_confirmation'}</t>
+          <t>platform_metrics_report_form_submit_confirmation_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'platform_metrics_report_form_submit_confirmation'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>platform_metrics_report_form_submit_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{'id':_16,_'name':_'platform_metrics_report_form_submit_confirmation_2'}</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{'id': 16, 'name': 'platform_metrics_report_form_submit_confirmation_2'}</t>
+          <t>platform metrics report form submit confirmation 2</t>
         </is>
       </c>
     </row>
